--- a/test/res/task.xlsx
+++ b/test/res/task.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\bite\Desktop\github\xlsx-exporter\test\res\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/codetypes/Desktop/Github/xlsx-exporter/test/res/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15740A5-6BED-40C9-84BB-8D7348EFD417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB5CD89-8AB6-3148-987F-0B4A6C468DF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-15" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="define" sheetId="9" r:id="rId1"/>
@@ -1100,7 +1100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="262">
   <si>
     <t>id</t>
   </si>
@@ -1891,17 +1891,23 @@
   <si>
     <t>id==item#*.id</t>
     <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>#define.value&amp;key1=TASK_TYPE</t>
+  </si>
+  <si>
+    <t>key2=MAIN==#main.type&amp;condition=mainline_event</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1930,7 +1936,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1950,7 +1956,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2236,7 +2242,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
   </cellStyles>
@@ -3162,17 +3168,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.625" customWidth="1"/>
-    <col min="3" max="3" width="16.625" customWidth="1"/>
-    <col min="4" max="4" width="25.625" customWidth="1"/>
-    <col min="5" max="5" width="45.875" customWidth="1"/>
-    <col min="6" max="6" width="18.625" customWidth="1"/>
-    <col min="8" max="9" width="12.625" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" customWidth="1"/>
+    <col min="5" max="5" width="45.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" customWidth="1"/>
+    <col min="8" max="9" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="42" t="s">
         <v>256</v>
       </c>
@@ -3182,7 +3188,7 @@
       <c r="E1" s="43"/>
       <c r="F1" s="43"/>
     </row>
-    <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="16">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3211,7 +3217,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="16">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -3240,7 +3246,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="16">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -3255,7 +3261,7 @@
       <c r="H4" s="34"/>
       <c r="I4" s="34"/>
     </row>
-    <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="16">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -3272,7 +3278,7 @@
         <v>13</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>13</v>
+        <v>261</v>
       </c>
       <c r="G5" s="33" t="s">
         <v>13</v>
@@ -3284,7 +3290,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="16">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -3301,7 +3307,7 @@
       <c r="H6" s="34"/>
       <c r="I6" s="34"/>
     </row>
-    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="16">
       <c r="A7" s="21" t="s">
         <v>17</v>
       </c>
@@ -3330,7 +3336,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="16">
       <c r="A8" s="21" t="s">
         <v>17</v>
       </c>
@@ -3353,7 +3359,7 @@
       <c r="H8" s="35"/>
       <c r="I8" s="35"/>
     </row>
-    <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="16">
       <c r="A9" s="21" t="s">
         <v>17</v>
       </c>
@@ -3376,7 +3382,7 @@
       <c r="H9" s="35"/>
       <c r="I9" s="35"/>
     </row>
-    <row r="10" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="16">
       <c r="A10" s="21" t="s">
         <v>17</v>
       </c>
@@ -3399,7 +3405,7 @@
       <c r="H10" s="35"/>
       <c r="I10" s="35"/>
     </row>
-    <row r="11" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="16">
       <c r="A11" s="21" t="s">
         <v>17</v>
       </c>
@@ -3422,7 +3428,7 @@
       <c r="H11" s="35"/>
       <c r="I11" s="35"/>
     </row>
-    <row r="12" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="16">
       <c r="A12" s="21" t="s">
         <v>17</v>
       </c>
@@ -3445,7 +3451,7 @@
       <c r="H12" s="35"/>
       <c r="I12" s="35"/>
     </row>
-    <row r="13" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="16">
       <c r="A13" s="21" t="s">
         <v>17</v>
       </c>
@@ -3468,7 +3474,7 @@
       <c r="H13" s="35"/>
       <c r="I13" s="35"/>
     </row>
-    <row r="14" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="16">
       <c r="A14" s="21" t="s">
         <v>17</v>
       </c>
@@ -3495,7 +3501,7 @@
       </c>
       <c r="I14" s="35"/>
     </row>
-    <row r="15" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="16">
       <c r="A15" s="21" t="s">
         <v>17</v>
       </c>
@@ -3518,7 +3524,7 @@
       <c r="H15" s="35"/>
       <c r="I15" s="35"/>
     </row>
-    <row r="16" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="16">
       <c r="A16" s="21" t="s">
         <v>17</v>
       </c>
@@ -3541,7 +3547,7 @@
       <c r="H16" s="35"/>
       <c r="I16" s="35"/>
     </row>
-    <row r="17" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="16">
       <c r="A17" s="21" t="s">
         <v>17</v>
       </c>
@@ -3564,7 +3570,7 @@
       <c r="H17" s="35"/>
       <c r="I17" s="35"/>
     </row>
-    <row r="18" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="16">
       <c r="A18" s="21" t="s">
         <v>17</v>
       </c>
@@ -3587,7 +3593,7 @@
       <c r="H18" s="35"/>
       <c r="I18" s="35"/>
     </row>
-    <row r="19" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="16">
       <c r="A19" s="21" t="s">
         <v>17</v>
       </c>
@@ -3610,7 +3616,7 @@
       <c r="H19" s="35"/>
       <c r="I19" s="35"/>
     </row>
-    <row r="20" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="16">
       <c r="A20" s="21" t="s">
         <v>17</v>
       </c>
@@ -3637,7 +3643,7 @@
       </c>
       <c r="I20" s="35"/>
     </row>
-    <row r="21" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="16">
       <c r="A21" s="21" t="s">
         <v>17</v>
       </c>
@@ -3660,7 +3666,7 @@
       <c r="H21" s="35"/>
       <c r="I21" s="35"/>
     </row>
-    <row r="22" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="16">
       <c r="A22" s="21" t="s">
         <v>17</v>
       </c>
@@ -3683,7 +3689,7 @@
       <c r="H22" s="35"/>
       <c r="I22" s="35"/>
     </row>
-    <row r="23" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="16">
       <c r="A23" s="21" t="s">
         <v>17</v>
       </c>
@@ -3706,7 +3712,7 @@
       <c r="H23" s="35"/>
       <c r="I23" s="35"/>
     </row>
-    <row r="24" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="16">
       <c r="A24" s="21" t="s">
         <v>17</v>
       </c>
@@ -3742,16 +3748,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{984B885C-48D0-4D9B-AAB3-39C5F463E278}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="41"/>
     <col min="2" max="2" width="32.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" s="44" t="s">
         <v>257</v>
       </c>
@@ -3760,7 +3766,7 @@
       <c r="D1" s="45"/>
       <c r="E1" s="45"/>
     </row>
-    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="16">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3777,7 +3783,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="16">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -3794,7 +3800,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="16">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -3803,7 +3809,7 @@
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="16">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -3820,7 +3826,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="16">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -3837,7 +3843,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7" s="41" t="s">
         <v>17</v>
       </c>
@@ -3854,7 +3860,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8" s="41" t="s">
         <v>17</v>
       </c>
@@ -3871,7 +3877,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9" s="41" t="s">
         <v>17</v>
       </c>
@@ -3889,7 +3895,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10" s="41" t="s">
         <v>17</v>
       </c>
@@ -3920,26 +3926,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:X17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="17.125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="17.875" style="9" customWidth="1"/>
-    <col min="3" max="4" width="15.125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="26.875" style="9" customWidth="1"/>
-    <col min="6" max="6" width="8.625" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="23.125" style="9" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="17.83203125" style="9" customWidth="1"/>
+    <col min="3" max="4" width="15.1640625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1640625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="23.1640625" style="9" customWidth="1"/>
     <col min="9" max="9" width="5" style="9" customWidth="1"/>
-    <col min="10" max="10" width="46.125" style="9" customWidth="1"/>
+    <col min="10" max="10" width="46.1640625" style="9" customWidth="1"/>
     <col min="11" max="11" width="31.5" style="9" customWidth="1"/>
     <col min="12" max="12" width="8" style="9" customWidth="1"/>
-    <col min="13" max="13" width="73.625" style="9" customWidth="1"/>
-    <col min="14" max="14" width="13.125" style="9" customWidth="1"/>
-    <col min="15" max="15" width="20.625" style="8" customWidth="1"/>
+    <col min="13" max="13" width="73.6640625" style="9" customWidth="1"/>
+    <col min="14" max="14" width="13.1640625" style="9" customWidth="1"/>
+    <col min="15" max="15" width="20.6640625" style="8" customWidth="1"/>
     <col min="16" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -4013,7 +4019,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24">
       <c r="A2" s="21" t="s">
         <v>22</v>
       </c>
@@ -4087,7 +4093,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24">
       <c r="A3" s="21" t="s">
         <v>12</v>
       </c>
@@ -4143,7 +4149,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24">
       <c r="A4" s="21" t="s">
         <v>14</v>
       </c>
@@ -4154,7 +4160,7 @@
         <v>254</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>260</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>13</v>
@@ -4217,7 +4223,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24">
       <c r="A5" s="21" t="s">
         <v>15</v>
       </c>
@@ -4289,7 +4295,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" ht="17">
       <c r="A6" s="24">
         <v>1001</v>
       </c>
@@ -4354,7 +4360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:24">
       <c r="A7" s="24">
         <v>1002</v>
       </c>
@@ -4414,7 +4420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" ht="17">
       <c r="A8" s="24">
         <v>1003</v>
       </c>
@@ -4479,7 +4485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" ht="17">
       <c r="A9" s="24">
         <v>1014</v>
       </c>
@@ -4541,7 +4547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24">
       <c r="A10" s="24">
         <v>100301</v>
       </c>
@@ -4611,7 +4617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" ht="17">
       <c r="A11" s="24">
         <v>100302</v>
       </c>
@@ -4671,7 +4677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24" s="20" customFormat="1" ht="17">
       <c r="A12" s="26">
         <v>100303</v>
       </c>
@@ -4731,7 +4737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24" ht="17">
       <c r="A13" s="24">
         <v>100001</v>
       </c>
@@ -4791,7 +4797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24">
       <c r="A14" s="24">
         <v>100002</v>
       </c>
@@ -4851,7 +4857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24">
       <c r="A15" s="24">
         <v>100003</v>
       </c>
@@ -4913,7 +4919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:24" ht="17">
       <c r="A16" s="24">
         <v>100304</v>
       </c>
@@ -4973,7 +4979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:23" ht="17">
       <c r="A17" s="24">
         <v>1013</v>
       </c>
@@ -5045,26 +5051,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:W16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="17.125" style="9" customWidth="1"/>
-    <col min="2" max="3" width="17.875" style="9" customWidth="1"/>
-    <col min="4" max="5" width="15.125" style="9" customWidth="1"/>
-    <col min="6" max="6" width="19.875" style="9" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" style="9" customWidth="1"/>
+    <col min="2" max="3" width="17.83203125" style="9" customWidth="1"/>
+    <col min="4" max="5" width="15.1640625" style="9" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" style="9" customWidth="1"/>
     <col min="7" max="7" width="28" style="9" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="9" customWidth="1"/>
-    <col min="9" max="9" width="23.125" style="9" customWidth="1"/>
-    <col min="10" max="10" width="16.125" style="9" customWidth="1"/>
-    <col min="11" max="11" width="63.125" style="9" customWidth="1"/>
-    <col min="12" max="12" width="20.125" style="9" customWidth="1"/>
-    <col min="13" max="13" width="13.125" style="9" customWidth="1"/>
+    <col min="8" max="8" width="15.1640625" style="9" customWidth="1"/>
+    <col min="9" max="9" width="23.1640625" style="9" customWidth="1"/>
+    <col min="10" max="10" width="16.1640625" style="9" customWidth="1"/>
+    <col min="11" max="11" width="63.1640625" style="9" customWidth="1"/>
+    <col min="12" max="12" width="20.1640625" style="9" customWidth="1"/>
+    <col min="13" max="13" width="13.1640625" style="9" customWidth="1"/>
     <col min="14" max="14" width="9" style="9"/>
-    <col min="15" max="15" width="13.125" style="9" customWidth="1"/>
+    <col min="15" max="15" width="13.1640625" style="9" customWidth="1"/>
     <col min="16" max="16" width="11" style="9" customWidth="1"/>
     <col min="17" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5132,7 +5138,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -5200,7 +5206,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -5251,7 +5257,7 @@
       </c>
       <c r="W3" s="1"/>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:23">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -5320,7 +5326,7 @@
       </c>
       <c r="W4" s="12"/>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:23">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -5386,7 +5392,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:23">
       <c r="A6" s="9">
         <f t="shared" ref="A6:A16" si="0">200000+C6*100+D6</f>
         <v>200101</v>
@@ -5443,7 +5449,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:23">
       <c r="A7" s="9">
         <f t="shared" si="0"/>
         <v>200102</v>
@@ -5499,7 +5505,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23">
       <c r="A8" s="9">
         <f t="shared" si="0"/>
         <v>200103</v>
@@ -5558,7 +5564,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:23">
       <c r="A9" s="9">
         <f t="shared" si="0"/>
         <v>200104</v>
@@ -5614,7 +5620,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:23">
       <c r="A10" s="9">
         <f t="shared" si="0"/>
         <v>200105</v>
@@ -5670,7 +5676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:23">
       <c r="A11" s="9">
         <f t="shared" si="0"/>
         <v>200106</v>
@@ -5726,7 +5732,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:23">
       <c r="A12" s="9">
         <f t="shared" si="0"/>
         <v>200107</v>
@@ -5782,7 +5788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:23">
       <c r="A13" s="9">
         <f t="shared" si="0"/>
         <v>200201</v>
@@ -5841,7 +5847,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:23">
       <c r="A14" s="9">
         <f t="shared" si="0"/>
         <v>200202</v>
@@ -5900,7 +5906,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23">
       <c r="A15" s="9">
         <f t="shared" si="0"/>
         <v>200203</v>
@@ -5959,7 +5965,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:23">
       <c r="A16" s="9">
         <f t="shared" si="0"/>
         <v>200204</v>
@@ -6029,16 +6035,16 @@
     <tabColor theme="5" tint="0.39915158543656726"/>
   </sheetPr>
   <dimension ref="A1:I19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="2" width="17.125" customWidth="1"/>
-    <col min="3" max="3" width="15.125" style="9" customWidth="1"/>
-    <col min="4" max="7" width="17.125" customWidth="1"/>
-    <col min="8" max="8" width="20.125" customWidth="1"/>
-    <col min="9" max="9" width="13.125" style="9" customWidth="1"/>
+    <col min="1" max="2" width="17.1640625" customWidth="1"/>
+    <col min="3" max="3" width="15.1640625" style="9" customWidth="1"/>
+    <col min="4" max="7" width="17.1640625" customWidth="1"/>
+    <col min="8" max="8" width="20.1640625" customWidth="1"/>
+    <col min="9" max="9" width="13.1640625" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="16.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6067,7 +6073,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="16.5">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -6096,7 +6102,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="16.5">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -6117,7 +6123,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="16.5">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -6146,7 +6152,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="16.5">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -6175,7 +6181,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
         <v>177</v>
       </c>
@@ -6204,7 +6210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
         <v>183</v>
       </c>
@@ -6233,7 +6239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9">
       <c r="A8" s="4" t="s">
         <v>188</v>
       </c>
@@ -6262,7 +6268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9">
       <c r="A9" s="4" t="s">
         <v>193</v>
       </c>
@@ -6291,7 +6297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9">
       <c r="A10" s="4"/>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
@@ -6302,7 +6308,7 @@
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
@@ -6313,7 +6319,7 @@
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="6"/>
@@ -6324,7 +6330,7 @@
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9">
       <c r="A13" s="4"/>
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
@@ -6335,7 +6341,7 @@
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9">
       <c r="A14" s="4"/>
       <c r="B14" s="5"/>
       <c r="C14" s="6"/>
@@ -6346,7 +6352,7 @@
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9">
       <c r="A15" s="4"/>
       <c r="B15" s="5"/>
       <c r="C15" s="6"/>
@@ -6357,7 +6363,7 @@
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9">
       <c r="A16" s="4"/>
       <c r="B16" s="5"/>
       <c r="C16" s="6"/>
@@ -6368,7 +6374,7 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9">
       <c r="A17" s="4"/>
       <c r="B17" s="5"/>
       <c r="C17" s="6"/>
@@ -6379,7 +6385,7 @@
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9">
       <c r="A18" s="4"/>
       <c r="B18" s="5"/>
       <c r="C18" s="6"/>
@@ -6390,7 +6396,7 @@
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9">
       <c r="A19" s="4"/>
       <c r="B19" s="5"/>
       <c r="C19" s="6"/>
@@ -6414,17 +6420,17 @@
     <tabColor theme="5" tint="0.39915158543656726"/>
   </sheetPr>
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultColWidth="17.125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="17.1640625" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="2" width="17.125" customWidth="1"/>
-    <col min="3" max="3" width="15.125" style="9" customWidth="1"/>
-    <col min="4" max="7" width="17.125" customWidth="1"/>
-    <col min="8" max="9" width="25.625" customWidth="1"/>
-    <col min="10" max="10" width="13.125" style="9" customWidth="1"/>
-    <col min="11" max="16377" width="17.125" customWidth="1"/>
+    <col min="1" max="2" width="17.1640625" customWidth="1"/>
+    <col min="3" max="3" width="15.1640625" style="9" customWidth="1"/>
+    <col min="4" max="7" width="17.1640625" customWidth="1"/>
+    <col min="8" max="9" width="25.6640625" customWidth="1"/>
+    <col min="10" max="10" width="13.1640625" style="9" customWidth="1"/>
+    <col min="11" max="16377" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="16.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6456,7 +6462,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="16.5">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -6488,7 +6494,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="16.5">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -6510,7 +6516,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="16.5">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -6542,7 +6548,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="16.5">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -6574,7 +6580,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
         <v>200</v>
       </c>
@@ -6606,7 +6612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
         <v>202</v>
       </c>
@@ -6638,7 +6644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
         <v>206</v>
       </c>
@@ -6670,7 +6676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
         <v>210</v>
       </c>
@@ -6702,7 +6708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10">
       <c r="A10" s="4"/>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
@@ -6714,7 +6720,7 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
@@ -6726,7 +6732,7 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="6"/>
@@ -6738,7 +6744,7 @@
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10">
       <c r="A13" s="4"/>
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
@@ -6750,7 +6756,7 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10">
       <c r="A14" s="4"/>
       <c r="B14" s="5"/>
       <c r="C14" s="6"/>
@@ -6762,19 +6768,19 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10">
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10">
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="10:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="10:10">
       <c r="J17" s="6"/>
     </row>
-    <row r="18" spans="10:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="10:10">
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="10:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="10:10">
       <c r="J19" s="6"/>
     </row>
   </sheetData>
@@ -6787,18 +6793,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
     <col min="5" max="5" width="29" customWidth="1"/>
-    <col min="6" max="6" width="20.875" customWidth="1"/>
-    <col min="7" max="7" width="16.625" customWidth="1"/>
-    <col min="9" max="9" width="35.625" customWidth="1"/>
-    <col min="10" max="10" width="21.875" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="35.6640625" customWidth="1"/>
+    <col min="10" max="10" width="21.83203125" customWidth="1"/>
     <col min="12" max="12" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6836,7 +6842,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="16">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -6874,7 +6880,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="16">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -6898,7 +6904,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="16">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -6936,7 +6942,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="16">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -6974,7 +6980,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" ht="16">
       <c r="A6" s="4" t="s">
         <v>215</v>
       </c>
@@ -7008,7 +7014,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" ht="16">
       <c r="A7" s="4" t="s">
         <v>221</v>
       </c>
@@ -7042,7 +7048,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="16">
       <c r="A8" s="4" t="s">
         <v>226</v>
       </c>
@@ -7076,7 +7082,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="16">
       <c r="A9" s="4" t="s">
         <v>231</v>
       </c>

--- a/test/res/task.xlsx
+++ b/test/res/task.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\bite\Desktop\github\xlsx-exporter\test\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1877A711-5BFE-48BD-9D6A-58D78B4ACC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F93D561-9D48-44CC-A724-6B5D31344B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-15" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="define" sheetId="9" r:id="rId1"/>
@@ -1101,7 +1101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="270">
   <si>
     <t>id</t>
   </si>
@@ -1920,6 +1920,10 @@
   </si>
   <si>
     <t>[]</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>task#*.id&amp;type=MAIN</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -3950,7 +3954,7 @@
     <col min="2" max="2" width="17.875" style="9" customWidth="1"/>
     <col min="3" max="4" width="15.125" style="9" customWidth="1"/>
     <col min="5" max="5" width="26.875" style="9" customWidth="1"/>
-    <col min="6" max="6" width="8.625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.75" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.125" style="9" customWidth="1"/>
     <col min="8" max="8" width="23.125" style="9" customWidth="1"/>
     <col min="9" max="9" width="5" style="9" customWidth="1"/>
@@ -4184,7 +4188,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>99</v>
+        <v>269</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>258</v>

--- a/test/res/task.xlsx
+++ b/test/res/task.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/codetypes/Desktop/Github/xlsx-exporter/test/res/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\bite\Desktop\github\typedsheet\test\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD05018-5370-084E-938D-63CC0632BB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E695B48-F084-4CE8-8832-120331F9B7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17680" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2580" yWindow="1290" windowWidth="34995" windowHeight="18885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="define" sheetId="9" r:id="rId1"/>
@@ -1936,7 +1936,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="279">
   <si>
     <t>id</t>
   </si>
@@ -2708,9 +2708,6 @@
     <t>#define.value&amp;key1=TASK_TYPE</t>
   </si>
   <si>
-    <t>$&amp;key2=MAIN==#main.type&amp;condition=mainline_event</t>
-  </si>
-  <si>
     <t>$[*].id==item#item.id</t>
   </si>
   <si>
@@ -2772,17 +2769,41 @@
   </si>
   <si>
     <t>TaskArgs?</t>
+  </si>
+  <si>
+    <t>checker</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>string?</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>检查</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>@refer(checker)</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>#main.id</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2811,7 +2832,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2831,7 +2852,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3111,7 +3132,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
   </cellStyles>
@@ -3398,6 +3419,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="level"/>
@@ -4036,20 +4058,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="25.6640625" customWidth="1"/>
-    <col min="5" max="5" width="45.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.6640625" customWidth="1"/>
-    <col min="8" max="9" width="12.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.625" customWidth="1"/>
+    <col min="3" max="3" width="16.625" customWidth="1"/>
+    <col min="4" max="4" width="25.625" customWidth="1"/>
+    <col min="5" max="5" width="45.875" customWidth="1"/>
+    <col min="6" max="6" width="18.625" customWidth="1"/>
+    <col min="8" max="8" width="33.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="40" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="41"/>
@@ -4057,7 +4080,7 @@
       <c r="E1" s="41"/>
       <c r="F1" s="41"/>
     </row>
-    <row r="2" spans="1:9" ht="16">
+    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4079,14 +4102,17 @@
       <c r="G2" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="I2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="32" t="s">
+      <c r="J2" s="32" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16">
+    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -4103,19 +4129,22 @@
         <v>10</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G3" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="31" t="s">
+        <v>274</v>
+      </c>
+      <c r="I3" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="J3" s="32" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16">
+    <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -4127,10 +4156,11 @@
       <c r="E4" s="31"/>
       <c r="F4" s="31"/>
       <c r="G4" s="31"/>
-      <c r="H4" s="32"/>
+      <c r="H4" s="31"/>
       <c r="I4" s="32"/>
-    </row>
-    <row r="5" spans="1:9" ht="16">
+      <c r="J4" s="32"/>
+    </row>
+    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -4147,19 +4177,22 @@
         <v>13</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="G5" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="32" t="s">
-        <v>13</v>
+      <c r="H5" s="31" t="s">
+        <v>275</v>
       </c>
       <c r="I5" s="32" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="16">
+      <c r="J5" s="32" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -4173,10 +4206,13 @@
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
-      <c r="H6" s="32"/>
+      <c r="H6" s="31" t="s">
+        <v>276</v>
+      </c>
       <c r="I6" s="32"/>
-    </row>
-    <row r="7" spans="1:9" ht="16">
+      <c r="J6" s="32"/>
+    </row>
+    <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="21" t="s">
         <v>17</v>
       </c>
@@ -4193,19 +4229,20 @@
         <v>21</v>
       </c>
       <c r="F7" s="11">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G7" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="33" t="s">
+      <c r="H7" s="11"/>
+      <c r="I7" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="33" t="s">
+      <c r="J7" s="33" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16">
+    <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
         <v>17</v>
       </c>
@@ -4225,10 +4262,11 @@
       <c r="G8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="33"/>
+      <c r="H8" s="11"/>
       <c r="I8" s="33"/>
-    </row>
-    <row r="9" spans="1:9" ht="16">
+      <c r="J8" s="33"/>
+    </row>
+    <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A9" s="21" t="s">
         <v>17</v>
       </c>
@@ -4248,10 +4286,11 @@
       <c r="G9" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H9" s="33"/>
+      <c r="H9" s="11"/>
       <c r="I9" s="33"/>
-    </row>
-    <row r="10" spans="1:9" ht="16">
+      <c r="J9" s="33"/>
+    </row>
+    <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A10" s="21" t="s">
         <v>17</v>
       </c>
@@ -4271,10 +4310,11 @@
       <c r="G10" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="33"/>
+      <c r="H10" s="11"/>
       <c r="I10" s="33"/>
-    </row>
-    <row r="11" spans="1:9" ht="16">
+      <c r="J10" s="33"/>
+    </row>
+    <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A11" s="21" t="s">
         <v>17</v>
       </c>
@@ -4294,10 +4334,11 @@
       <c r="G11" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="33"/>
+      <c r="H11" s="11"/>
       <c r="I11" s="33"/>
-    </row>
-    <row r="12" spans="1:9" ht="16">
+      <c r="J11" s="33"/>
+    </row>
+    <row r="12" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A12" s="21" t="s">
         <v>17</v>
       </c>
@@ -4317,10 +4358,11 @@
       <c r="G12" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H12" s="33"/>
+      <c r="H12" s="11"/>
       <c r="I12" s="33"/>
-    </row>
-    <row r="13" spans="1:9" ht="16">
+      <c r="J12" s="33"/>
+    </row>
+    <row r="13" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A13" s="21" t="s">
         <v>17</v>
       </c>
@@ -4340,10 +4382,11 @@
       <c r="G13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H13" s="33"/>
+      <c r="H13" s="11"/>
       <c r="I13" s="33"/>
-    </row>
-    <row r="14" spans="1:9" ht="16">
+      <c r="J13" s="33"/>
+    </row>
+    <row r="14" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A14" s="21" t="s">
         <v>17</v>
       </c>
@@ -4365,12 +4408,13 @@
       <c r="G14" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="33" t="s">
+      <c r="H14" s="11"/>
+      <c r="I14" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="I14" s="33"/>
-    </row>
-    <row r="15" spans="1:9" ht="16">
+      <c r="J14" s="33"/>
+    </row>
+    <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A15" s="21" t="s">
         <v>17</v>
       </c>
@@ -4390,10 +4434,11 @@
       <c r="G15" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H15" s="33"/>
+      <c r="H15" s="11"/>
       <c r="I15" s="33"/>
-    </row>
-    <row r="16" spans="1:9" ht="16">
+      <c r="J15" s="33"/>
+    </row>
+    <row r="16" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A16" s="21" t="s">
         <v>17</v>
       </c>
@@ -4413,10 +4458,11 @@
       <c r="G16" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="33"/>
+      <c r="H16" s="11"/>
       <c r="I16" s="33"/>
-    </row>
-    <row r="17" spans="1:9" ht="16">
+      <c r="J16" s="33"/>
+    </row>
+    <row r="17" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A17" s="21" t="s">
         <v>17</v>
       </c>
@@ -4436,10 +4482,11 @@
       <c r="G17" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="33"/>
+      <c r="H17" s="11"/>
       <c r="I17" s="33"/>
-    </row>
-    <row r="18" spans="1:9" ht="16">
+      <c r="J17" s="33"/>
+    </row>
+    <row r="18" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A18" s="21" t="s">
         <v>17</v>
       </c>
@@ -4459,10 +4506,11 @@
       <c r="G18" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H18" s="33"/>
+      <c r="H18" s="11"/>
       <c r="I18" s="33"/>
-    </row>
-    <row r="19" spans="1:9" ht="16">
+      <c r="J18" s="33"/>
+    </row>
+    <row r="19" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A19" s="21" t="s">
         <v>17</v>
       </c>
@@ -4482,10 +4530,11 @@
       <c r="G19" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="33"/>
+      <c r="H19" s="11"/>
       <c r="I19" s="33"/>
-    </row>
-    <row r="20" spans="1:9" ht="16">
+      <c r="J19" s="33"/>
+    </row>
+    <row r="20" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A20" s="21" t="s">
         <v>17</v>
       </c>
@@ -4507,12 +4556,13 @@
       <c r="G20" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H20" s="33" t="s">
+      <c r="H20" s="11"/>
+      <c r="I20" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="I20" s="33"/>
-    </row>
-    <row r="21" spans="1:9" ht="16">
+      <c r="J20" s="33"/>
+    </row>
+    <row r="21" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A21" s="21" t="s">
         <v>17</v>
       </c>
@@ -4532,10 +4582,11 @@
       <c r="G21" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H21" s="33"/>
+      <c r="H21" s="11"/>
       <c r="I21" s="33"/>
-    </row>
-    <row r="22" spans="1:9" ht="16">
+      <c r="J21" s="33"/>
+    </row>
+    <row r="22" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A22" s="21" t="s">
         <v>17</v>
       </c>
@@ -4555,10 +4606,11 @@
       <c r="G22" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H22" s="33"/>
+      <c r="H22" s="11"/>
       <c r="I22" s="33"/>
-    </row>
-    <row r="23" spans="1:9" ht="16">
+      <c r="J22" s="33"/>
+    </row>
+    <row r="23" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A23" s="21" t="s">
         <v>17</v>
       </c>
@@ -4578,10 +4630,11 @@
       <c r="G23" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H23" s="33"/>
+      <c r="H23" s="11"/>
       <c r="I23" s="33"/>
-    </row>
-    <row r="24" spans="1:9" ht="16">
+      <c r="J23" s="33"/>
+    </row>
+    <row r="24" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A24" s="21" t="s">
         <v>17</v>
       </c>
@@ -4596,13 +4649,16 @@
         <v>72</v>
       </c>
       <c r="F24" s="35">
-        <v>1023</v>
+        <v>1013</v>
       </c>
       <c r="G24" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="H24" s="34"/>
+      <c r="H24" s="35" t="s">
+        <v>278</v>
+      </c>
       <c r="I24" s="34"/>
+      <c r="J24" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4617,16 +4673,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{984B885C-48D0-4D9B-AAB3-39C5F463E278}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="39"/>
     <col min="2" max="2" width="32.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="42" t="s">
         <v>251</v>
       </c>
@@ -4635,7 +4691,7 @@
       <c r="D1" s="43"/>
       <c r="E1" s="43"/>
     </row>
-    <row r="2" spans="1:5" ht="16">
+    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4652,7 +4708,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="16">
+    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -4669,7 +4725,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16">
+    <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -4678,7 +4734,7 @@
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" ht="16">
+    <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -4695,7 +4751,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16">
+    <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -4712,7 +4768,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="39" t="s">
         <v>17</v>
       </c>
@@ -4729,7 +4785,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="39" t="s">
         <v>17</v>
       </c>
@@ -4746,7 +4802,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="39" t="s">
         <v>17</v>
       </c>
@@ -4764,7 +4820,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="39" t="s">
         <v>17</v>
       </c>
@@ -4795,26 +4851,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:X17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.1640625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="17.83203125" style="9" customWidth="1"/>
-    <col min="3" max="4" width="15.1640625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" style="9" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1640625" style="9" customWidth="1"/>
-    <col min="8" max="8" width="23.1640625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="17.125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="17.875" style="9" customWidth="1"/>
+    <col min="3" max="4" width="15.125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="26.875" style="9" customWidth="1"/>
+    <col min="6" max="6" width="19.625" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.125" style="9" customWidth="1"/>
+    <col min="8" max="8" width="23.125" style="9" customWidth="1"/>
     <col min="9" max="9" width="5" style="9" customWidth="1"/>
-    <col min="10" max="10" width="46.1640625" style="9" customWidth="1"/>
+    <col min="10" max="10" width="46.125" style="9" customWidth="1"/>
     <col min="11" max="11" width="31.5" style="9" customWidth="1"/>
     <col min="12" max="12" width="8" style="9" customWidth="1"/>
-    <col min="13" max="13" width="73.6640625" style="9" customWidth="1"/>
-    <col min="14" max="14" width="13.1640625" style="9" customWidth="1"/>
-    <col min="15" max="15" width="20.6640625" style="8" customWidth="1"/>
+    <col min="13" max="13" width="73.625" style="9" customWidth="1"/>
+    <col min="14" max="14" width="13.125" style="9" customWidth="1"/>
+    <col min="15" max="15" width="20.625" style="8" customWidth="1"/>
     <col min="16" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -4888,7 +4944,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
         <v>22</v>
       </c>
@@ -4899,7 +4955,7 @@
         <v>22</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>11</v>
@@ -4908,7 +4964,7 @@
         <v>94</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>11</v>
@@ -4962,7 +5018,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="21" t="s">
         <v>12</v>
       </c>
@@ -5018,7 +5074,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="21" t="s">
         <v>14</v>
       </c>
@@ -5035,10 +5091,10 @@
         <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>13</v>
@@ -5092,7 +5148,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" s="21" t="s">
         <v>15</v>
       </c>
@@ -5164,7 +5220,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="17">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="22">
         <v>1001</v>
       </c>
@@ -5185,7 +5241,7 @@
         <v>1002</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H6" s="16" t="s">
         <v>38</v>
@@ -5231,7 +5287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="22">
         <v>1002</v>
       </c>
@@ -5291,7 +5347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="17">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A8" s="22">
         <v>1003</v>
       </c>
@@ -5356,7 +5412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="17">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" s="22">
         <v>1014</v>
       </c>
@@ -5377,7 +5433,7 @@
         <v>100301</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H9" s="16" t="s">
         <v>57</v>
@@ -5418,7 +5474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="22">
         <v>100301</v>
       </c>
@@ -5439,7 +5495,7 @@
         <v>100302</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>38</v>
@@ -5488,7 +5544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="17">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="22">
         <v>100302</v>
       </c>
@@ -5548,7 +5604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="20" customFormat="1" ht="17">
+    <row r="12" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="24">
         <v>100303</v>
       </c>
@@ -5608,7 +5664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="17">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="22">
         <v>100001</v>
       </c>
@@ -5668,7 +5724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="22">
         <v>100002</v>
       </c>
@@ -5728,7 +5784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" s="22">
         <v>100003</v>
       </c>
@@ -5790,7 +5846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="17">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" s="22">
         <v>100304</v>
       </c>
@@ -5850,7 +5906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="17">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A17" s="22">
         <v>1013</v>
       </c>
@@ -5922,27 +5978,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:X16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.1640625" style="9" customWidth="1"/>
-    <col min="2" max="3" width="17.83203125" style="9" customWidth="1"/>
-    <col min="4" max="5" width="15.1640625" style="9" customWidth="1"/>
-    <col min="6" max="6" width="19.83203125" style="9" customWidth="1"/>
+    <col min="1" max="1" width="17.125" style="9" customWidth="1"/>
+    <col min="2" max="3" width="17.875" style="9" customWidth="1"/>
+    <col min="4" max="5" width="15.125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="19.875" style="9" customWidth="1"/>
     <col min="7" max="7" width="28" style="9" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" style="9" customWidth="1"/>
-    <col min="9" max="9" width="23.1640625" style="9" customWidth="1"/>
-    <col min="10" max="10" width="16.1640625" style="9" customWidth="1"/>
-    <col min="11" max="11" width="63.1640625" style="9" customWidth="1"/>
-    <col min="12" max="12" width="8.83203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.1640625" style="9" customWidth="1"/>
-    <col min="14" max="14" width="13.1640625" style="9" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="9" customWidth="1"/>
+    <col min="9" max="9" width="23.125" style="9" customWidth="1"/>
+    <col min="10" max="10" width="16.125" style="9" customWidth="1"/>
+    <col min="11" max="11" width="63.125" style="9" customWidth="1"/>
+    <col min="12" max="12" width="8.875" style="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.125" style="9" customWidth="1"/>
+    <col min="14" max="14" width="13.125" style="9" customWidth="1"/>
     <col min="15" max="15" width="9" style="9"/>
-    <col min="16" max="16" width="13.1640625" style="9" customWidth="1"/>
+    <col min="16" max="16" width="13.125" style="9" customWidth="1"/>
     <col min="17" max="17" width="11" style="9" customWidth="1"/>
     <col min="18" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5977,7 +6033,7 @@
         <v>8</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>80</v>
@@ -6013,7 +6069,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -6027,7 +6083,7 @@
         <v>22</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>11</v>
@@ -6045,7 +6101,7 @@
         <v>95</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>11</v>
@@ -6084,7 +6140,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -6136,7 +6192,7 @@
       </c>
       <c r="X3" s="1"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -6174,7 +6230,7 @@
         <v>13</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>13</v>
@@ -6208,7 +6264,7 @@
       </c>
       <c r="X4" s="12"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -6243,7 +6299,7 @@
         <v>109</v>
       </c>
       <c r="L5" s="13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="M5" s="13" t="s">
         <v>110</v>
@@ -6277,7 +6333,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
         <f t="shared" ref="A6:A16" si="0">200000+C6*100+D6</f>
         <v>200101</v>
@@ -6337,7 +6393,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
         <f t="shared" si="0"/>
         <v>200102</v>
@@ -6396,7 +6452,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <f t="shared" si="0"/>
         <v>200103</v>
@@ -6458,7 +6514,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <f t="shared" si="0"/>
         <v>200104</v>
@@ -6517,7 +6573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
         <f t="shared" si="0"/>
         <v>200105</v>
@@ -6576,7 +6632,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
         <f t="shared" si="0"/>
         <v>200106</v>
@@ -6635,7 +6691,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
         <f t="shared" si="0"/>
         <v>200107</v>
@@ -6694,7 +6750,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <f t="shared" si="0"/>
         <v>200201</v>
@@ -6756,7 +6812,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="9">
         <f t="shared" si="0"/>
         <v>200202</v>
@@ -6818,7 +6874,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
         <f t="shared" si="0"/>
         <v>200203</v>
@@ -6880,7 +6936,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <f t="shared" si="0"/>
         <v>200204</v>
@@ -6953,17 +7009,17 @@
     <tabColor theme="5" tint="0.39915158543656726"/>
   </sheetPr>
   <dimension ref="A1:J19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="17.1640625" customWidth="1"/>
-    <col min="3" max="3" width="15.1640625" style="9" customWidth="1"/>
-    <col min="4" max="7" width="17.1640625" customWidth="1"/>
-    <col min="8" max="8" width="20.1640625" customWidth="1"/>
-    <col min="9" max="9" width="13.1640625" style="9" customWidth="1"/>
-    <col min="10" max="10" width="39.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="17.125" customWidth="1"/>
+    <col min="3" max="3" width="15.125" style="9" customWidth="1"/>
+    <col min="4" max="7" width="17.125" customWidth="1"/>
+    <col min="8" max="8" width="20.125" customWidth="1"/>
+    <col min="9" max="9" width="13.125" style="9" customWidth="1"/>
+    <col min="10" max="10" width="39.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6992,10 +7048,10 @@
         <v>81</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -7024,10 +7080,10 @@
         <v>11</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -7049,7 +7105,7 @@
       </c>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -7081,7 +7137,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -7113,7 +7169,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>175</v>
       </c>
@@ -7142,10 +7198,10 @@
         <v>0</v>
       </c>
       <c r="J6" s="19" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>181</v>
       </c>
@@ -7174,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>186</v>
       </c>
@@ -7206,7 +7262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>191</v>
       </c>
@@ -7235,7 +7291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="4"/>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
@@ -7246,7 +7302,7 @@
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
@@ -7257,7 +7313,7 @@
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="6"/>
@@ -7268,7 +7324,7 @@
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="4"/>
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
@@ -7279,7 +7335,7 @@
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="4"/>
       <c r="B14" s="5"/>
       <c r="C14" s="6"/>
@@ -7290,7 +7346,7 @@
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="4"/>
       <c r="B15" s="5"/>
       <c r="C15" s="6"/>
@@ -7301,7 +7357,7 @@
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="4"/>
       <c r="B16" s="5"/>
       <c r="C16" s="6"/>
@@ -7312,7 +7368,7 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="4"/>
       <c r="B17" s="5"/>
       <c r="C17" s="6"/>
@@ -7323,7 +7379,7 @@
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="4"/>
       <c r="B18" s="5"/>
       <c r="C18" s="6"/>
@@ -7334,7 +7390,7 @@
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="4"/>
       <c r="B19" s="5"/>
       <c r="C19" s="6"/>
@@ -7359,17 +7415,17 @@
     <tabColor theme="5" tint="0.39915158543656726"/>
   </sheetPr>
   <dimension ref="A1:J19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="17.1640625" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="17.125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="17.1640625" customWidth="1"/>
-    <col min="3" max="3" width="15.1640625" style="9" customWidth="1"/>
-    <col min="4" max="7" width="17.1640625" customWidth="1"/>
-    <col min="8" max="9" width="25.6640625" customWidth="1"/>
-    <col min="10" max="10" width="13.1640625" style="9" customWidth="1"/>
-    <col min="11" max="16377" width="17.1640625" customWidth="1"/>
+    <col min="1" max="2" width="17.125" customWidth="1"/>
+    <col min="3" max="3" width="15.125" style="9" customWidth="1"/>
+    <col min="4" max="7" width="17.125" customWidth="1"/>
+    <col min="8" max="9" width="25.625" customWidth="1"/>
+    <col min="10" max="10" width="13.125" style="9" customWidth="1"/>
+    <col min="11" max="16377" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.5">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7401,7 +7457,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16.5">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -7433,7 +7489,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16.5">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -7455,7 +7511,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="16.5">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -7478,16 +7534,16 @@
         <v>13</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>256</v>
-      </c>
       <c r="J4" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="16.5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -7519,7 +7575,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>198</v>
       </c>
@@ -7551,7 +7607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>200</v>
       </c>
@@ -7583,7 +7639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>204</v>
       </c>
@@ -7615,7 +7671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>208</v>
       </c>
@@ -7647,7 +7703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="4"/>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
@@ -7659,7 +7715,7 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
@@ -7671,7 +7727,7 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="6"/>
@@ -7683,7 +7739,7 @@
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="4"/>
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
@@ -7695,7 +7751,7 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="4"/>
       <c r="B14" s="5"/>
       <c r="C14" s="6"/>
@@ -7707,19 +7763,19 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="10:10">
+    <row r="17" spans="10:10" x14ac:dyDescent="0.35">
       <c r="J17" s="6"/>
     </row>
-    <row r="18" spans="10:10">
+    <row r="18" spans="10:10" x14ac:dyDescent="0.35">
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="10:10">
+    <row r="19" spans="10:10" x14ac:dyDescent="0.35">
       <c r="J19" s="6"/>
     </row>
   </sheetData>
@@ -7732,18 +7788,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.625" customWidth="1"/>
     <col min="5" max="5" width="29" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="9" max="9" width="35.6640625" customWidth="1"/>
-    <col min="10" max="10" width="21.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.875" customWidth="1"/>
+    <col min="7" max="7" width="16.625" customWidth="1"/>
+    <col min="9" max="9" width="35.625" customWidth="1"/>
+    <col min="10" max="10" width="21.875" customWidth="1"/>
     <col min="12" max="12" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16">
+    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7781,7 +7837,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="16">
+    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -7819,7 +7875,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="16">
+    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -7843,7 +7899,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="16">
+    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -7881,7 +7937,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="16">
+    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -7919,7 +7975,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="16">
+    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>213</v>
       </c>
@@ -7953,7 +8009,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="16">
+    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>219</v>
       </c>
@@ -7987,7 +8043,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="16">
+    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>224</v>
       </c>
@@ -8021,7 +8077,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="16">
+    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>229</v>
       </c>
